--- a/zernovye_2026.xlsx
+++ b/zernovye_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.170.200\обмен\НеезжаловаАВ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F5EBEFE-0C6A-4C04-9A2A-0B95E3C38A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{159D4509-0F4E-4C2E-AD58-1A7284DB9218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="836" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="836" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ИНФО" sheetId="17" r:id="rId1"/>
@@ -274,7 +274,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="479">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1543" uniqueCount="480">
   <si>
     <t>Показатели</t>
   </si>
@@ -1711,6 +1711,9 @@
   </si>
   <si>
     <t>1ед.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2 / 10</t>
   </si>
 </sst>
 </file>
@@ -6573,6 +6576,12 @@
     <xf numFmtId="177" fontId="50" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="10" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="41" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6584,12 +6593,6 @@
     </xf>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="41" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2860">
@@ -11610,7 +11613,7 @@
                   <c:v>18818.61</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6116.31</c:v>
+                  <c:v>7754.31</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11766,7 +11769,7 @@
                   <c:v>4163</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>903</c:v>
+                  <c:v>1149</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11940,7 +11943,7 @@
                   <c:v>45.204443910641366</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>67.733222591362122</c:v>
+                  <c:v>67.487467362924278</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -21935,7 +21938,7 @@
                 <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:rPr>
               <a:pPr algn="r"/>
-              <a:t>6 116 т</a:t>
+              <a:t>7 754 т</a:t>
             </a:fld>
             <a:endParaRPr lang="ru-RU" sz="2000" b="0">
               <a:solidFill>
@@ -22224,7 +22227,7 @@
                   <a:cs typeface="Arial"/>
                 </a:rPr>
                 <a:pPr algn="r"/>
-                <a:t>25,2%</a:t>
+                <a:t>31,9%</a:t>
               </a:fld>
               <a:endParaRPr lang="ru-RU" sz="2000" b="1">
                 <a:solidFill>
@@ -27143,50 +27146,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:42" ht="46.5" thickBot="1">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="159" t="s">
         <v>477</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
-      <c r="G2" s="157"/>
-      <c r="H2" s="157"/>
-      <c r="I2" s="157"/>
-      <c r="J2" s="157"/>
-      <c r="K2" s="157"/>
-      <c r="L2" s="157"/>
-      <c r="M2" s="157"/>
-      <c r="N2" s="157"/>
-      <c r="O2" s="157"/>
-      <c r="P2" s="157"/>
-      <c r="Q2" s="157"/>
-      <c r="R2" s="157"/>
-      <c r="S2" s="157"/>
-      <c r="T2" s="157"/>
-      <c r="U2" s="157"/>
-      <c r="V2" s="157"/>
-      <c r="W2" s="157"/>
-      <c r="X2" s="157"/>
-      <c r="Y2" s="157"/>
-      <c r="Z2" s="157"/>
-      <c r="AA2" s="157"/>
-      <c r="AB2" s="157"/>
-      <c r="AC2" s="157"/>
-      <c r="AD2" s="157"/>
-      <c r="AE2" s="157"/>
-      <c r="AF2" s="157"/>
-      <c r="AG2" s="157"/>
-      <c r="AH2" s="157"/>
-      <c r="AI2" s="157"/>
-      <c r="AJ2" s="157"/>
-      <c r="AK2" s="157"/>
-      <c r="AL2" s="157"/>
-      <c r="AM2" s="157"/>
-      <c r="AN2" s="157"/>
-      <c r="AO2" s="157"/>
-      <c r="AP2" s="157"/>
+      <c r="B2" s="159"/>
+      <c r="C2" s="159"/>
+      <c r="D2" s="159"/>
+      <c r="E2" s="159"/>
+      <c r="F2" s="159"/>
+      <c r="G2" s="159"/>
+      <c r="H2" s="159"/>
+      <c r="I2" s="159"/>
+      <c r="J2" s="159"/>
+      <c r="K2" s="159"/>
+      <c r="L2" s="159"/>
+      <c r="M2" s="159"/>
+      <c r="N2" s="159"/>
+      <c r="O2" s="159"/>
+      <c r="P2" s="159"/>
+      <c r="Q2" s="159"/>
+      <c r="R2" s="159"/>
+      <c r="S2" s="159"/>
+      <c r="T2" s="159"/>
+      <c r="U2" s="159"/>
+      <c r="V2" s="159"/>
+      <c r="W2" s="159"/>
+      <c r="X2" s="159"/>
+      <c r="Y2" s="159"/>
+      <c r="Z2" s="159"/>
+      <c r="AA2" s="159"/>
+      <c r="AB2" s="159"/>
+      <c r="AC2" s="159"/>
+      <c r="AD2" s="159"/>
+      <c r="AE2" s="159"/>
+      <c r="AF2" s="159"/>
+      <c r="AG2" s="159"/>
+      <c r="AH2" s="159"/>
+      <c r="AI2" s="159"/>
+      <c r="AJ2" s="159"/>
+      <c r="AK2" s="159"/>
+      <c r="AL2" s="159"/>
+      <c r="AM2" s="159"/>
+      <c r="AN2" s="159"/>
+      <c r="AO2" s="159"/>
+      <c r="AP2" s="159"/>
     </row>
     <row r="3" spans="1:42" ht="36" customHeight="1" thickTop="1"/>
     <row r="4" spans="1:42" ht="15.75" customHeight="1"/>
@@ -27537,50 +27540,50 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:25" ht="27.75">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="161" t="s">
         <v>474</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
-      <c r="Q2" s="159"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="159"/>
-      <c r="T2" s="159"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="161"/>
+      <c r="S2" s="161"/>
+      <c r="T2" s="161"/>
       <c r="U2" s="62"/>
       <c r="V2" s="62"/>
     </row>
     <row r="3" spans="2:25" ht="18" customHeight="1">
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="159"/>
-      <c r="O3" s="159"/>
-      <c r="P3" s="159"/>
-      <c r="Q3" s="159"/>
-      <c r="R3" s="159"/>
-      <c r="S3" s="159"/>
-      <c r="T3" s="159"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="161"/>
+      <c r="K3" s="161"/>
+      <c r="L3" s="161"/>
+      <c r="M3" s="161"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="161"/>
+      <c r="P3" s="161"/>
+      <c r="Q3" s="161"/>
+      <c r="R3" s="161"/>
+      <c r="S3" s="161"/>
+      <c r="T3" s="161"/>
     </row>
     <row r="4" spans="2:25">
       <c r="I4" s="149" t="s">
@@ -28087,8 +28090,8 @@
         <v>0</v>
       </c>
       <c r="D23" s="25"/>
-      <c r="E23" s="158"/>
-      <c r="F23" s="158"/>
+      <c r="E23" s="160"/>
+      <c r="F23" s="160"/>
     </row>
     <row r="24" spans="2:25" ht="13.9" customHeight="1">
       <c r="B24" s="11" t="s">
@@ -28101,8 +28104,8 @@
     </row>
     <row r="37" spans="21:22" ht="15.75" customHeight="1"/>
     <row r="38" spans="21:22">
-      <c r="U38" s="160"/>
-      <c r="V38" s="160"/>
+      <c r="U38" s="162"/>
+      <c r="V38" s="162"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -28145,48 +28148,48 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" ht="27.75">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
-      <c r="Q2" s="159"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="159"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="161"/>
+      <c r="S2" s="161"/>
       <c r="T2" s="62"/>
       <c r="U2" s="62"/>
     </row>
     <row r="3" spans="2:21" ht="18" customHeight="1">
-      <c r="B3" s="159"/>
-      <c r="C3" s="159"/>
-      <c r="D3" s="159"/>
-      <c r="E3" s="159"/>
-      <c r="F3" s="159"/>
-      <c r="G3" s="159"/>
-      <c r="H3" s="159"/>
-      <c r="I3" s="159"/>
-      <c r="J3" s="159"/>
-      <c r="K3" s="159"/>
-      <c r="L3" s="159"/>
-      <c r="M3" s="159"/>
-      <c r="N3" s="159"/>
-      <c r="O3" s="159"/>
-      <c r="P3" s="159"/>
-      <c r="Q3" s="159"/>
-      <c r="R3" s="159"/>
-      <c r="S3" s="159"/>
+      <c r="B3" s="161"/>
+      <c r="C3" s="161"/>
+      <c r="D3" s="161"/>
+      <c r="E3" s="161"/>
+      <c r="F3" s="161"/>
+      <c r="G3" s="161"/>
+      <c r="H3" s="161"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="161"/>
+      <c r="K3" s="161"/>
+      <c r="L3" s="161"/>
+      <c r="M3" s="161"/>
+      <c r="N3" s="161"/>
+      <c r="O3" s="161"/>
+      <c r="P3" s="161"/>
+      <c r="Q3" s="161"/>
+      <c r="R3" s="161"/>
+      <c r="S3" s="161"/>
     </row>
     <row r="5" spans="2:21" s="4" customFormat="1" ht="28.5">
       <c r="B5" s="9" t="s">
@@ -28794,8 +28797,8 @@
         <v>1</v>
       </c>
       <c r="D25" s="25"/>
-      <c r="E25" s="158"/>
-      <c r="F25" s="158"/>
+      <c r="E25" s="160"/>
+      <c r="F25" s="160"/>
       <c r="K25" s="51">
         <v>45538</v>
       </c>
@@ -29079,10 +29082,10 @@
       <c r="S40" s="27">
         <v>0.26100000000000001</v>
       </c>
-      <c r="T40" s="160" t="s">
+      <c r="T40" s="162" t="s">
         <v>101</v>
       </c>
-      <c r="U40" s="160"/>
+      <c r="U40" s="162"/>
     </row>
     <row r="41" spans="11:21">
       <c r="K41" s="63">
@@ -35912,24 +35915,24 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:26" ht="27.75" customHeight="1">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="161" t="s">
         <v>467</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
-      <c r="Q2" s="159"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
@@ -36465,8 +36468,8 @@
         <f>C21/C20</f>
         <v>0</v>
       </c>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
+      <c r="E24" s="160"/>
+      <c r="F24" s="160"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -36504,23 +36507,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:25" ht="27.75" customHeight="1">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="161" t="s">
         <v>469</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
       <c r="Q2" s="62"/>
       <c r="R2" s="62"/>
       <c r="S2" s="62"/>
@@ -37033,8 +37036,8 @@
         <f>IFERROR(C21/C20,)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="158"/>
-      <c r="F24" s="158"/>
+      <c r="E24" s="160"/>
+      <c r="F24" s="160"/>
     </row>
     <row r="27" spans="2:21">
       <c r="M27" s="42"/>
@@ -37999,27 +38002,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:27" ht="27.75" customHeight="1">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="161" t="s">
         <v>475</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
-      <c r="Q2" s="159"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="159"/>
-      <c r="T2" s="159"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="161"/>
+      <c r="S2" s="161"/>
+      <c r="T2" s="161"/>
       <c r="U2" s="75"/>
       <c r="V2" s="30"/>
       <c r="W2" s="30"/>
@@ -38446,10 +38449,10 @@
         <v>0.21133333333333335</v>
       </c>
       <c r="Z10" s="155">
-        <f>AVERAGE(780,770,780)</f>
-        <v>776.66666666666663</v>
-      </c>
-      <c r="AA10" s="161">
+        <f>AVERAGE(780,773,768)</f>
+        <v>773.66666666666663</v>
+      </c>
+      <c r="AA10" s="157">
         <f>AVERAGE(0.2%,0,0)</f>
         <v>6.6666666666666664E-4</v>
       </c>
@@ -38478,15 +38481,21 @@
       </c>
       <c r="I11" s="95">
         <f>C21</f>
-        <v>6116.31</v>
-      </c>
-      <c r="M11" s="36"/>
+        <v>7754.31</v>
+      </c>
+      <c r="M11" s="36">
+        <v>46209</v>
+      </c>
       <c r="N11" s="37"/>
-      <c r="O11" s="89"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="156">
+      <c r="O11" s="89">
+        <v>246</v>
+      </c>
+      <c r="P11" s="32">
+        <v>1638000</v>
+      </c>
+      <c r="Q11" s="57">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>66.58536585365853</v>
       </c>
       <c r="R11" s="36"/>
       <c r="S11" s="37"/>
@@ -38496,11 +38505,26 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="W11" s="36"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="89"/>
-      <c r="Z11" s="32"/>
-      <c r="AA11" s="57"/>
+      <c r="W11" s="150">
+        <f>AVERAGE(0.129,0.123,0.125,0.128)</f>
+        <v>0.12625</v>
+      </c>
+      <c r="X11" s="151">
+        <f>AVERAGE(0.145,0.128,0.124,0.144)</f>
+        <v>0.13525000000000001</v>
+      </c>
+      <c r="Y11" s="150">
+        <f>AVERAGE(0.2,0.208,0.211,0.219)</f>
+        <v>0.20949999999999999</v>
+      </c>
+      <c r="Z11" s="155">
+        <f>AVERAGE(780,770,780,812)</f>
+        <v>785.5</v>
+      </c>
+      <c r="AA11" s="157">
+        <f>AVERAGE(0,0,0,0.6%)</f>
+        <v>1.5E-3</v>
+      </c>
     </row>
     <row r="12" spans="2:27">
       <c r="B12" s="11" t="s">
@@ -38573,7 +38597,7 @@
       </c>
       <c r="I13" s="96">
         <f>O20</f>
-        <v>903</v>
+        <v>1149</v>
       </c>
       <c r="M13" s="36"/>
       <c r="N13" s="37"/>
@@ -38621,7 +38645,7 @@
       </c>
       <c r="I14" s="97">
         <f>Q20</f>
-        <v>67.733222591362122</v>
+        <v>67.487467362924278</v>
       </c>
       <c r="M14" s="36"/>
       <c r="N14" s="37"/>
@@ -38645,7 +38669,7 @@
       <c r="Z14" s="32"/>
       <c r="AA14" s="57"/>
     </row>
-    <row r="15" spans="2:27" ht="15" customHeight="1">
+    <row r="15" spans="2:27" ht="21.75" customHeight="1">
       <c r="B15" s="11" t="s">
         <v>16</v>
       </c>
@@ -38668,7 +38692,7 @@
         <v>41.5</v>
       </c>
       <c r="I15" s="97">
-        <v>60.4</v>
+        <v>61</v>
       </c>
       <c r="J15" s="76"/>
       <c r="M15" s="36"/>
@@ -38716,7 +38740,7 @@
         <v>409</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>106</v>
+        <v>479</v>
       </c>
       <c r="J16" s="76"/>
       <c r="M16" s="36"/>
@@ -38845,15 +38869,15 @@
       <c r="N20" s="86"/>
       <c r="O20" s="90">
         <f>SUM(O6:O19)</f>
-        <v>903</v>
+        <v>1149</v>
       </c>
       <c r="P20" s="87">
         <f>SUM(P6:P19)</f>
-        <v>6116310</v>
+        <v>7754310</v>
       </c>
       <c r="Q20" s="88">
         <f>P20/O20/100</f>
-        <v>67.733222591362122</v>
+        <v>67.487467362924278</v>
       </c>
       <c r="R20" s="86" t="s">
         <v>40</v>
@@ -38873,23 +38897,23 @@
       </c>
       <c r="W20" s="153">
         <f>AVERAGE(W6:W19)</f>
-        <v>0.12610000000000002</v>
+        <v>0.12612500000000001</v>
       </c>
       <c r="X20" s="153">
         <f>AVERAGE(X6:X19)</f>
-        <v>0.12493333333333334</v>
+        <v>0.12665277777777778</v>
       </c>
       <c r="Y20" s="153">
         <f>AVERAGE(Y6:Y19)</f>
-        <v>0.22416666666666668</v>
+        <v>0.22172222222222224</v>
       </c>
       <c r="Z20" s="154">
         <f>AVERAGE(Z6:Z19)</f>
-        <v>764.6</v>
-      </c>
-      <c r="AA20" s="162">
+        <v>767.58333333333337</v>
+      </c>
+      <c r="AA20" s="158">
         <f>AVERAGE(AA6:AA19)</f>
-        <v>1.3333333333333334E-4</v>
+        <v>3.6111111111111109E-4</v>
       </c>
     </row>
     <row r="21" spans="2:27" ht="15">
@@ -38898,11 +38922,11 @@
       </c>
       <c r="C21" s="73">
         <f>P20/1000</f>
-        <v>6116.31</v>
+        <v>7754.31</v>
       </c>
       <c r="D21" s="74">
         <f>C21/I13*10</f>
-        <v>67.733222591362136</v>
+        <v>67.487467362924292</v>
       </c>
     </row>
     <row r="22" spans="2:27">
@@ -38917,7 +38941,7 @@
       </c>
       <c r="C23" s="19">
         <f>I13/I12</f>
-        <v>0.2377567140600316</v>
+        <v>0.30252764612954186</v>
       </c>
       <c r="G23" s="26"/>
       <c r="H23" s="26"/>
@@ -38929,7 +38953,7 @@
       </c>
       <c r="C24" s="19">
         <f>IFERROR(C21/C20,0)</f>
-        <v>0.25162544431279621</v>
+        <v>0.31901288507109005</v>
       </c>
       <c r="G24" s="38"/>
       <c r="H24" s="38"/>
@@ -39052,27 +39076,27 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="27.75" customHeight="1">
-      <c r="B2" s="159" t="s">
+      <c r="B2" s="161" t="s">
         <v>470</v>
       </c>
-      <c r="C2" s="159"/>
-      <c r="D2" s="159"/>
-      <c r="E2" s="159"/>
-      <c r="F2" s="159"/>
-      <c r="G2" s="159"/>
-      <c r="H2" s="159"/>
-      <c r="I2" s="159"/>
-      <c r="J2" s="159"/>
-      <c r="K2" s="159"/>
-      <c r="L2" s="159"/>
-      <c r="M2" s="159"/>
-      <c r="N2" s="159"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
-      <c r="Q2" s="159"/>
-      <c r="R2" s="159"/>
-      <c r="S2" s="159"/>
-      <c r="T2" s="159"/>
+      <c r="C2" s="161"/>
+      <c r="D2" s="161"/>
+      <c r="E2" s="161"/>
+      <c r="F2" s="161"/>
+      <c r="G2" s="161"/>
+      <c r="H2" s="161"/>
+      <c r="I2" s="161"/>
+      <c r="J2" s="161"/>
+      <c r="K2" s="161"/>
+      <c r="L2" s="161"/>
+      <c r="M2" s="161"/>
+      <c r="N2" s="161"/>
+      <c r="O2" s="161"/>
+      <c r="P2" s="161"/>
+      <c r="Q2" s="161"/>
+      <c r="R2" s="161"/>
+      <c r="S2" s="161"/>
+      <c r="T2" s="161"/>
       <c r="U2" s="62"/>
       <c r="V2" s="62"/>
       <c r="W2" s="62"/>
@@ -39688,9 +39712,9 @@
       </c>
     </row>
     <row r="22" spans="2:20" ht="14.25" customHeight="1">
-      <c r="E22" s="158"/>
-      <c r="F22" s="158"/>
-      <c r="G22" s="158"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="160"/>
       <c r="H22" s="45"/>
     </row>
     <row r="23" spans="2:20">
